--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -646,7 +646,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Tabs: Dashboard summarises the data automatically; Revision history records changes to this file.</t>
+          <t>Tabs: Revision history records changes to this file.</t>
         </is>
       </c>
     </row>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/templates/project-brief-template/project-brief-template-expert.xlsx
+++ b/templates/project-brief-template/project-brief-template-expert.xlsx
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
